--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440418</v>
       </c>
       <c r="B2" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440418</v>
       </c>
       <c r="B2" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440418</v>
       </c>
       <c r="B2" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440418</v>
       </c>
       <c r="B2" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440418</v>
       </c>
       <c r="B2" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440418</v>
       </c>
       <c r="B2" t="n">
-        <v>78164</v>
+        <v>78171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440418</v>
       </c>
       <c r="B2" t="n">
-        <v>78171</v>
+        <v>78173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440418</v>
       </c>
       <c r="B2" t="n">
-        <v>78173</v>
+        <v>78201</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,516 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125007168</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ö Fått, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>748876</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7192698</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125007166</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ö Fått, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>748995</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7192659</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125007030</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ö Fått, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>748969</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7192620</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125007165</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ö Fått, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>748943</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7192599</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125007167</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ö Fått, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>748912</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7192670</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125007168</v>
+        <v>125007030</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748876</v>
+        <v>748969</v>
       </c>
       <c r="R3" t="n">
-        <v>7192698</v>
+        <v>7192620</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007030</v>
+        <v>125007165</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748969</v>
+        <v>748943</v>
       </c>
       <c r="R5" t="n">
-        <v>7192620</v>
+        <v>7192599</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125007165</v>
+        <v>125007167</v>
       </c>
       <c r="B6" t="n">
         <v>92293</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748943</v>
+        <v>748912</v>
       </c>
       <c r="R6" t="n">
-        <v>7192599</v>
+        <v>7192670</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125007167</v>
+        <v>125007168</v>
       </c>
       <c r="B7" t="n">
         <v>92293</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748912</v>
+        <v>748876</v>
       </c>
       <c r="R7" t="n">
-        <v>7192670</v>
+        <v>7192698</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007166</v>
+        <v>125007168</v>
       </c>
       <c r="B4" t="n">
         <v>92293</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748995</v>
+        <v>748876</v>
       </c>
       <c r="R4" t="n">
-        <v>7192659</v>
+        <v>7192698</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125007167</v>
+        <v>125007166</v>
       </c>
       <c r="B6" t="n">
         <v>92293</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748912</v>
+        <v>748995</v>
       </c>
       <c r="R6" t="n">
-        <v>7192670</v>
+        <v>7192659</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125007168</v>
+        <v>125007167</v>
       </c>
       <c r="B7" t="n">
         <v>92293</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748876</v>
+        <v>748912</v>
       </c>
       <c r="R7" t="n">
-        <v>7192698</v>
+        <v>7192670</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125007030</v>
+        <v>125007165</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748969</v>
+        <v>748943</v>
       </c>
       <c r="R3" t="n">
-        <v>7192620</v>
+        <v>7192599</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007168</v>
+        <v>125007167</v>
       </c>
       <c r="B4" t="n">
         <v>92293</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748876</v>
+        <v>748912</v>
       </c>
       <c r="R4" t="n">
-        <v>7192698</v>
+        <v>7192670</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007165</v>
+        <v>125007030</v>
       </c>
       <c r="B5" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748943</v>
+        <v>748969</v>
       </c>
       <c r="R5" t="n">
-        <v>7192599</v>
+        <v>7192620</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125007167</v>
+        <v>125007168</v>
       </c>
       <c r="B7" t="n">
         <v>92293</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748912</v>
+        <v>748876</v>
       </c>
       <c r="R7" t="n">
-        <v>7192670</v>
+        <v>7192698</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007167</v>
+        <v>125007168</v>
       </c>
       <c r="B4" t="n">
         <v>92293</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748912</v>
+        <v>748876</v>
       </c>
       <c r="R4" t="n">
-        <v>7192670</v>
+        <v>7192698</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007030</v>
+        <v>125007167</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748969</v>
+        <v>748912</v>
       </c>
       <c r="R5" t="n">
-        <v>7192620</v>
+        <v>7192670</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125007166</v>
+        <v>125007030</v>
       </c>
       <c r="B6" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748995</v>
+        <v>748969</v>
       </c>
       <c r="R6" t="n">
-        <v>7192659</v>
+        <v>7192620</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125007168</v>
+        <v>125007166</v>
       </c>
       <c r="B7" t="n">
         <v>92293</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748876</v>
+        <v>748995</v>
       </c>
       <c r="R7" t="n">
-        <v>7192698</v>
+        <v>7192659</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125007165</v>
+        <v>125007167</v>
       </c>
       <c r="B3" t="n">
         <v>92293</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748943</v>
+        <v>748912</v>
       </c>
       <c r="R3" t="n">
-        <v>7192599</v>
+        <v>7192670</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007168</v>
+        <v>125007165</v>
       </c>
       <c r="B4" t="n">
         <v>92293</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748876</v>
+        <v>748943</v>
       </c>
       <c r="R4" t="n">
-        <v>7192698</v>
+        <v>7192599</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007167</v>
+        <v>125007168</v>
       </c>
       <c r="B5" t="n">
         <v>92293</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748912</v>
+        <v>748876</v>
       </c>
       <c r="R5" t="n">
-        <v>7192670</v>
+        <v>7192698</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125007030</v>
+        <v>125007166</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748969</v>
+        <v>748995</v>
       </c>
       <c r="R6" t="n">
-        <v>7192620</v>
+        <v>7192659</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125007166</v>
+        <v>125007030</v>
       </c>
       <c r="B7" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748995</v>
+        <v>748969</v>
       </c>
       <c r="R7" t="n">
-        <v>7192659</v>
+        <v>7192620</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007165</v>
+        <v>125007166</v>
       </c>
       <c r="B4" t="n">
         <v>92293</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748943</v>
+        <v>748995</v>
       </c>
       <c r="R4" t="n">
-        <v>7192599</v>
+        <v>7192659</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007168</v>
+        <v>125007165</v>
       </c>
       <c r="B5" t="n">
         <v>92293</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748876</v>
+        <v>748943</v>
       </c>
       <c r="R5" t="n">
-        <v>7192698</v>
+        <v>7192599</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125007166</v>
+        <v>125007030</v>
       </c>
       <c r="B6" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748995</v>
+        <v>748969</v>
       </c>
       <c r="R6" t="n">
-        <v>7192659</v>
+        <v>7192620</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125007030</v>
+        <v>125007168</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748969</v>
+        <v>748876</v>
       </c>
       <c r="R7" t="n">
-        <v>7192620</v>
+        <v>7192698</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125007167</v>
+        <v>125007030</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748912</v>
+        <v>748969</v>
       </c>
       <c r="R3" t="n">
-        <v>7192670</v>
+        <v>7192620</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007166</v>
+        <v>125007168</v>
       </c>
       <c r="B4" t="n">
         <v>92293</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748995</v>
+        <v>748876</v>
       </c>
       <c r="R4" t="n">
-        <v>7192659</v>
+        <v>7192698</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007165</v>
+        <v>125007166</v>
       </c>
       <c r="B5" t="n">
         <v>92293</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748943</v>
+        <v>748995</v>
       </c>
       <c r="R5" t="n">
-        <v>7192599</v>
+        <v>7192659</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125007030</v>
+        <v>125007167</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748969</v>
+        <v>748912</v>
       </c>
       <c r="R6" t="n">
-        <v>7192620</v>
+        <v>7192670</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125007168</v>
+        <v>125007165</v>
       </c>
       <c r="B7" t="n">
         <v>92293</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748876</v>
+        <v>748943</v>
       </c>
       <c r="R7" t="n">
-        <v>7192698</v>
+        <v>7192599</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125007030</v>
+        <v>125007168</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748969</v>
+        <v>748876</v>
       </c>
       <c r="R3" t="n">
-        <v>7192620</v>
+        <v>7192698</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007168</v>
+        <v>125007167</v>
       </c>
       <c r="B4" t="n">
         <v>92293</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748876</v>
+        <v>748912</v>
       </c>
       <c r="R4" t="n">
-        <v>7192698</v>
+        <v>7192670</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125007167</v>
+        <v>125007030</v>
       </c>
       <c r="B6" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748912</v>
+        <v>748969</v>
       </c>
       <c r="R6" t="n">
-        <v>7192670</v>
+        <v>7192620</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125007168</v>
+        <v>125007167</v>
       </c>
       <c r="B3" t="n">
         <v>92293</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748876</v>
+        <v>748912</v>
       </c>
       <c r="R3" t="n">
-        <v>7192698</v>
+        <v>7192670</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007167</v>
+        <v>125007168</v>
       </c>
       <c r="B4" t="n">
         <v>92293</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748912</v>
+        <v>748876</v>
       </c>
       <c r="R4" t="n">
-        <v>7192670</v>
+        <v>7192698</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007166</v>
+        <v>125007165</v>
       </c>
       <c r="B5" t="n">
         <v>92293</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748995</v>
+        <v>748943</v>
       </c>
       <c r="R5" t="n">
-        <v>7192659</v>
+        <v>7192599</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125007165</v>
+        <v>125007166</v>
       </c>
       <c r="B7" t="n">
         <v>92293</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748943</v>
+        <v>748995</v>
       </c>
       <c r="R7" t="n">
-        <v>7192599</v>
+        <v>7192659</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125007167</v>
+        <v>125007030</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748912</v>
+        <v>748969</v>
       </c>
       <c r="R3" t="n">
-        <v>7192670</v>
+        <v>7192620</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
         <v>125007168</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>92448</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007165</v>
+        <v>125007166</v>
       </c>
       <c r="B5" t="n">
-        <v>92293</v>
+        <v>92448</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748943</v>
+        <v>748995</v>
       </c>
       <c r="R5" t="n">
-        <v>7192599</v>
+        <v>7192659</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125007030</v>
+        <v>125007167</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>92448</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748969</v>
+        <v>748912</v>
       </c>
       <c r="R6" t="n">
-        <v>7192620</v>
+        <v>7192670</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125007166</v>
+        <v>125007165</v>
       </c>
       <c r="B7" t="n">
-        <v>92293</v>
+        <v>92448</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748995</v>
+        <v>748943</v>
       </c>
       <c r="R7" t="n">
-        <v>7192659</v>
+        <v>7192599</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125007030</v>
+        <v>125007168</v>
       </c>
       <c r="B3" t="n">
-        <v>78947</v>
+        <v>92448</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748969</v>
+        <v>748876</v>
       </c>
       <c r="R3" t="n">
-        <v>7192620</v>
+        <v>7192698</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007168</v>
+        <v>125007030</v>
       </c>
       <c r="B4" t="n">
-        <v>92448</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748876</v>
+        <v>748969</v>
       </c>
       <c r="R4" t="n">
-        <v>7192698</v>
+        <v>7192620</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007030</v>
+        <v>125007166</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
+        <v>92448</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748969</v>
+        <v>748995</v>
       </c>
       <c r="R4" t="n">
-        <v>7192620</v>
+        <v>7192659</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007166</v>
+        <v>125007030</v>
       </c>
       <c r="B5" t="n">
-        <v>92448</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748995</v>
+        <v>748969</v>
       </c>
       <c r="R5" t="n">
-        <v>7192659</v>
+        <v>7192620</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125007167</v>
+        <v>125007165</v>
       </c>
       <c r="B6" t="n">
         <v>92448</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748912</v>
+        <v>748943</v>
       </c>
       <c r="R6" t="n">
-        <v>7192670</v>
+        <v>7192599</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125007165</v>
+        <v>125007167</v>
       </c>
       <c r="B7" t="n">
         <v>92448</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748943</v>
+        <v>748912</v>
       </c>
       <c r="R7" t="n">
-        <v>7192599</v>
+        <v>7192670</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 53137-2022 artfynd.xlsx
+++ b/artfynd/A 53137-2022 artfynd.xlsx
@@ -782,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125007168</v>
+        <v>125007030</v>
       </c>
       <c r="B3" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748876</v>
+        <v>748969</v>
       </c>
       <c r="R3" t="n">
-        <v>7192698</v>
+        <v>7192620</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,16 +879,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125007166</v>
+        <v>125007167</v>
       </c>
       <c r="B4" t="n">
         <v>92448</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>LC</t>
@@ -924,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748995</v>
+        <v>748912</v>
       </c>
       <c r="R4" t="n">
-        <v>7192659</v>
+        <v>7192670</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,37 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125007030</v>
+        <v>125007166</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748969</v>
+        <v>748995</v>
       </c>
       <c r="R5" t="n">
-        <v>7192620</v>
+        <v>7192659</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,11 +1078,6 @@
       <c r="B6" t="n">
         <v>92448</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1190,16 +1170,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125007167</v>
+        <v>125007168</v>
       </c>
       <c r="B7" t="n">
         <v>92448</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1230,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748912</v>
+        <v>748876</v>
       </c>
       <c r="R7" t="n">
-        <v>7192670</v>
+        <v>7192698</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
